--- a/rubric/feedback.xlsx
+++ b/rubric/feedback.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="160">
   <si>
     <t>Total</t>
   </si>
@@ -51,7 +51,10 @@
     <t>Communication (30%)</t>
   </si>
   <si>
-    <t>Final mark</t>
+    <t>Provisional final grade (A3)</t>
+  </si>
+  <si>
+    <t>Final grade (A4)</t>
   </si>
   <si>
     <t>Grade</t>
@@ -105,23 +108,19 @@
     <t>Unable to place the research in a wider context, no clear literature research</t>
   </si>
   <si>
-    <t>Sufficient introduction and justification of the research topic, but superficial (limited
-literature review)</t>
-  </si>
-  <si>
-    <t>Sufficient introduction and justification of the research topic, with fair literature
-support (decent literature review)</t>
-  </si>
-  <si>
-    <t>Good introduction and justification of the research topic with supporting literature
-(but not all included)</t>
+    <t>Sufficient introduction and justification of the research topic, but superficial (limited literature review)</t>
+  </si>
+  <si>
+    <t>Sufficient introduction and justification of the research topic, with fair literature support (decent literature review)</t>
+  </si>
+  <si>
+    <t>Good introduction and justification of the research topic with supporting literature (but not all included)</t>
   </si>
   <si>
     <t>Good introduction and justification of the research topic, with vast literature support</t>
   </si>
   <si>
-    <t>Excellent introduction and justification of the research topic, with all literature
-support</t>
+    <t>Excellent introduction and justification of the research topic, with all literature support</t>
   </si>
   <si>
     <t>Choices of methods / data</t>
@@ -209,7 +208,7 @@
     <t>Autonomy / proactiveness</t>
   </si>
   <si>
-    <t>Not autonomus or proactive at all</t>
+    <t>Not autonomous or proactive at all</t>
   </si>
   <si>
     <t>Sometimes autonomous and proactive, but generally needed steering by supervisors. Rarely came up with creative new ideas and new sources of information.</t>
@@ -306,8 +305,7 @@
     <t>Prepared a good and feasible plan at the beginning of the research project, which was mostly followed or adjusted when needed (e.g. according to progress and new findings).</t>
   </si>
   <si>
-    <t>Prepared a clear and feasible plan at the beginning of the research project, which was followed and
-improved when needed (e.g. according to progress and new findings).</t>
+    <t>Prepared a clear and feasible plan at the beginning of the research project, which was followed and improved when needed (e.g. according to progress and new findings).</t>
   </si>
   <si>
     <t>Prepared an efficient, clear and feasible plan at the beginning of the research project, which was followed and improved when needed (e.g. according to progress and new findings)</t>
@@ -391,15 +389,13 @@
     <t>Report properly acknowledges other work most of the time and contains a mostly complete list of references</t>
   </si>
   <si>
-    <t>Report properly acknowledges other work everywhere and contains a complete and well-formatted list of
-references</t>
+    <t>Report properly acknowledges other work everywhere and contains a complete and well-formatted list of references</t>
   </si>
   <si>
     <t>Supplementary output / data</t>
   </si>
   <si>
-    <t>Work yields some other output (e.g. software, data), which is added to the report and published in an ad hoc
-manner</t>
+    <t>Work yields some other output (e.g. software, data), which is added to the report and published in an ad hoc manner</t>
   </si>
   <si>
     <t>Work attempts to yield other output (e.g. software, data) whenever possible, which is published following open science best practices (e.g. fully available source code on public repository with documentation and sample data)</t>
@@ -1813,11 +1809,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:D3"/>
+  <dimension ref="A2:E3"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="4" width="16.3516" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="16.3516" style="1" customWidth="1"/>
+    <col min="1" max="5" width="16.3516" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="16.3516" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.65" customHeight="1">
@@ -1827,6 +1823,7 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" ht="32.25" customHeight="1">
       <c r="A2" t="s" s="3">
@@ -1840,6 +1837,9 @@
       </c>
       <c r="D2" t="s" s="3">
         <v>4</v>
+      </c>
+      <c r="E2" t="s" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="3" ht="20.25" customHeight="1">
@@ -1859,10 +1859,14 @@
         <f t="array" ref="D3">A3*0.5+B3*0.2+C3*0.3</f>
         <v>0</v>
       </c>
+      <c r="E3" s="5" cm="1">
+        <f t="array" ref="E3">D3</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.277778" footer="0.277778"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="72" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
@@ -1878,8 +1882,7 @@
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="16.3516" style="6" customWidth="1"/>
-    <col min="2" max="2" width="6.35156" style="6" customWidth="1"/>
-    <col min="3" max="8" width="25" style="6" customWidth="1"/>
+    <col min="2" max="8" width="25" style="6" customWidth="1"/>
     <col min="9" max="16384" width="16.3516" style="6" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1898,10 +1901,10 @@
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="7"/>
       <c r="B2" t="s" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="9">
         <v>6</v>
@@ -1921,174 +1924,174 @@
     </row>
     <row r="3" ht="38.3" customHeight="1">
       <c r="A3" t="s" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
       <c r="D3" t="s" s="13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s" s="13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s" s="13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s" s="13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3" t="s" s="13">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="38.1" customHeight="1">
       <c r="A4" t="s" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" t="s" s="16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s" s="16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s" s="16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s" s="16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s" s="16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s" s="16">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" ht="48.1" customHeight="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" ht="38.1" customHeight="1">
       <c r="A5" t="s" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" t="s" s="16">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s" s="16">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s" s="16">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s" s="16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s" s="16">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5" t="s" s="16">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="38.1" customHeight="1">
       <c r="A6" t="s" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" t="s" s="16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s" s="16">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s" s="16">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s" s="16">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" t="s" s="16">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s" s="16">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="58.1" customHeight="1">
       <c r="A7" t="s" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="17"/>
       <c r="D7" t="s" s="16">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s" s="16">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s" s="16">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7" t="s" s="16">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H7" t="s" s="16">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" ht="48.1" customHeight="1">
       <c r="A8" t="s" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" t="s" s="16">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s" s="16">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s" s="16">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s" s="16">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G8" t="s" s="16">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s" s="16">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" ht="68.1" customHeight="1">
       <c r="A9" t="s" s="14">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" t="s" s="16">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s" s="16">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s" s="16">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F9" t="s" s="16">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G9" t="s" s="16">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H9" t="s" s="16">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" ht="44.05" customHeight="1">
       <c r="A10" t="s" s="14">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s" s="18">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="19"/>
@@ -2117,8 +2120,7 @@
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="16.3516" style="20" customWidth="1"/>
-    <col min="2" max="2" width="6.35156" style="20" customWidth="1"/>
-    <col min="3" max="8" width="25" style="20" customWidth="1"/>
+    <col min="2" max="8" width="25" style="20" customWidth="1"/>
     <col min="9" max="16384" width="16.3516" style="20" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2137,10 +2139,10 @@
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="7"/>
       <c r="B2" t="s" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="9">
         <v>6</v>
@@ -2160,130 +2162,130 @@
     </row>
     <row r="3" ht="78.3" customHeight="1">
       <c r="A3" t="s" s="10">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" t="s" s="13">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s" s="13">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s" s="13">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F3" t="s" s="13">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" t="s" s="13">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H3" t="s" s="13">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" ht="78.1" customHeight="1">
       <c r="A4" t="s" s="14">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" t="s" s="16">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s" s="16">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s" s="16">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F4" t="s" s="16">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G4" t="s" s="16">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H4" t="s" s="16">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" ht="38.1" customHeight="1">
       <c r="A5" t="s" s="14">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" t="s" s="16">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s" s="16">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s" s="16">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F5" t="s" s="16">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G5" t="s" s="16">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H5" t="s" s="16">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" ht="48.1" customHeight="1">
       <c r="A6" t="s" s="14">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" t="s" s="16">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s" s="16">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s" s="16">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F6" t="s" s="16">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G6" t="s" s="16">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s" s="16">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" ht="58.1" customHeight="1">
       <c r="A7" t="s" s="14">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7" s="15"/>
       <c r="C7" t="s" s="16">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s" s="16">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s" s="16">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s" s="16">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G7" t="s" s="16">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H7" t="s" s="16">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" ht="44.05" customHeight="1">
       <c r="A8" t="s" s="14">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s" s="18">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="19"/>
@@ -2312,14 +2314,13 @@
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="16.3516" style="21" customWidth="1"/>
-    <col min="2" max="2" width="6.35156" style="21" customWidth="1"/>
-    <col min="3" max="8" width="25" style="21" customWidth="1"/>
+    <col min="2" max="8" width="25" style="21" customWidth="1"/>
     <col min="9" max="16384" width="16.3516" style="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.65" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2332,10 +2333,10 @@
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="7"/>
       <c r="B2" t="s" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="9">
         <v>6</v>
@@ -2355,115 +2356,115 @@
     </row>
     <row r="3" ht="38.3" customHeight="1">
       <c r="A3" t="s" s="10">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" t="s" s="13">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s" s="13">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s" s="13">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F3" t="s" s="13">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G3" t="s" s="13">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H3" t="s" s="13">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" ht="48.1" customHeight="1">
       <c r="A4" t="s" s="14">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" t="s" s="16">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s" s="16">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s" s="16">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F4" t="s" s="16">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G4" t="s" s="16">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H4" t="s" s="16">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" ht="58.1" customHeight="1">
       <c r="A5" t="s" s="14">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="17"/>
       <c r="D5" s="17"/>
       <c r="E5" t="s" s="16">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F5" t="s" s="16">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G5" t="s" s="16">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H5" t="s" s="16">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" ht="28.1" customHeight="1">
       <c r="A6" t="s" s="14">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
       <c r="E6" t="s" s="16">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F6" t="s" s="16">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G6" t="s" s="16">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H6" t="s" s="16">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" ht="48.1" customHeight="1">
       <c r="A7" t="s" s="14">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" t="s" s="16">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F7" t="s" s="16">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G7" t="s" s="16">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H7" t="s" s="16">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" ht="78.1" customHeight="1">
       <c r="A8" t="s" s="14">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="17"/>
@@ -2471,18 +2472,18 @@
       <c r="E8" s="17"/>
       <c r="F8" s="17"/>
       <c r="G8" t="s" s="16">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H8" t="s" s="16">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" ht="44.05" customHeight="1">
       <c r="A9" t="s" s="14">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s" s="18">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" s="19"/>
       <c r="D9" s="19"/>
@@ -2511,14 +2512,13 @@
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="16.3516" style="22" customWidth="1"/>
-    <col min="2" max="2" width="6.35156" style="22" customWidth="1"/>
-    <col min="3" max="8" width="25" style="22" customWidth="1"/>
+    <col min="2" max="8" width="25" style="22" customWidth="1"/>
     <col min="9" max="16384" width="16.3516" style="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.65" customHeight="1">
       <c r="A1" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2531,10 +2531,10 @@
     <row r="2" ht="20.25" customHeight="1">
       <c r="A2" s="7"/>
       <c r="B2" t="s" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="9">
         <v>6</v>
@@ -2554,152 +2554,152 @@
     </row>
     <row r="3" ht="38.3" customHeight="1">
       <c r="A3" t="s" s="10">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" t="s" s="13">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D3" t="s" s="13">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s" s="13">
+        <v>123</v>
+      </c>
+      <c r="F3" t="s" s="13">
         <v>122</v>
       </c>
-      <c r="F3" t="s" s="13">
-        <v>121</v>
-      </c>
       <c r="G3" t="s" s="13">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H3" t="s" s="13">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" ht="48.1" customHeight="1">
       <c r="A4" t="s" s="14">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" t="s" s="16">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D4" t="s" s="16">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E4" t="s" s="16">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F4" t="s" s="16">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G4" t="s" s="16">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H4" t="s" s="16">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" ht="28.1" customHeight="1">
       <c r="A5" t="s" s="14">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="17"/>
       <c r="D5" t="s" s="16">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s" s="16">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F5" t="s" s="16">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G5" t="s" s="16">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H5" t="s" s="16">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" ht="68.1" customHeight="1">
       <c r="A6" t="s" s="14">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" t="s" s="16">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s" s="16">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s" s="16">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F6" t="s" s="16">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G6" t="s" s="16">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H6" t="s" s="16">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" ht="38.1" customHeight="1">
       <c r="A7" t="s" s="14">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B7" s="15"/>
       <c r="C7" t="s" s="16">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D7" t="s" s="16">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E7" t="s" s="16">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F7" t="s" s="16">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G7" t="s" s="16">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H7" t="s" s="16">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" ht="28.1" customHeight="1">
       <c r="A8" t="s" s="14">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" t="s" s="16">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D8" t="s" s="16">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E8" t="s" s="16">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F8" t="s" s="16">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G8" t="s" s="16">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H8" t="s" s="16">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" ht="44.05" customHeight="1">
       <c r="A9" t="s" s="14">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B9" t="s" s="18">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" s="19"/>
       <c r="D9" s="19"/>
